--- a/site/assets/project_meridian_model.xlsx
+++ b/site/assets/project_meridian_model.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>949.2</v>
+        <v>953.2</v>
       </c>
     </row>
     <row r="3">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>137598.1098091472</v>
+        <v>137586.9290431072</v>
       </c>
     </row>
     <row r="10">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>332.25</v>
+        <v>347.6</v>
       </c>
     </row>
     <row r="12">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>372.12</v>
+        <v>389.31</v>
       </c>
     </row>
     <row r="20">
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -869,6 +869,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -917,6 +918,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -945,9 +951,6 @@
       <c r="F2" t="n">
         <v/>
       </c>
-      <c r="G2" t="n">
-        <v/>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>completed</t>
@@ -956,6 +959,11 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>ILLUSTRATIVE — verify; government divestment auction</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.nseindia.com/companies-listing/corporate-filings-announcements</t>
         </is>
       </c>
     </row>
@@ -986,9 +994,6 @@
       <c r="F3" t="n">
         <v>9.9</v>
       </c>
-      <c r="G3" t="n">
-        <v/>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>withdrawn</t>
@@ -997,6 +1002,11 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>ILLUSTRATIVE — verify; delisting offer failed on reverse book building</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.sebi.gov.in/filings/takeovers.html</t>
         </is>
       </c>
     </row>
@@ -1027,9 +1037,6 @@
       <c r="F4" t="n">
         <v/>
       </c>
-      <c r="G4" t="n">
-        <v>7.5</v>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>completed</t>
@@ -1037,7 +1044,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE — verify; IBC resolution (approval 2019; closed 2021)</t>
+          <t>VERIFIED — IBC resolution; NCLT approved Rs 19700 cr plan (Rs 19350 cr to financial creditors = 41% recovery on Rs 47158 cr claims) Sep 2019; closed Mar 2021; Supreme Court declared plan illegal and ordered liquidation May 2025; EV/EBITDA unverified</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/companies/news/sc-rejects-jsw-steel-bhushan-power-resolution-plan-liquidation-125050201442_1.html</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1697,7 @@
         <v/>
       </c>
       <c r="F3" s="14">
-        <f>B3-61.170952657320115</f>
+        <f>B3-60.19575756232558</f>
         <v/>
       </c>
     </row>
@@ -1731,7 +1743,7 @@
         <v/>
       </c>
       <c r="F5" s="14">
-        <f>B5-0.021489195947387074</f>
+        <f>B5-0.005204485472821707</f>
         <v/>
       </c>
     </row>
@@ -1878,7 +1890,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Acquiring 51% crosses the 25% threshold -&gt; mandatory open offer for 26% of the target at the floor price (modeled at the Rs 372 offer price; real floor is the highest-of tests incl. 60-day VWAP).</t>
+          <t>Acquiring 51% crosses the 25% threshold -&gt; mandatory open offer for 26% of the target at the floor price (modeled at the Rs 389 offer price; real floor is the highest-of tests incl. 60-day VWAP).</t>
         </is>
       </c>
     </row>
@@ -1892,14 +1904,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>50% acceptance: buy 23.88 Cr shares for Rs 8,885 Cr; post-offer holding 64.0%.</t>
+          <t>50% acceptance: buy 23.88 Cr shares for Rs 9,295 Cr; post-offer holding 64.0%.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>100% acceptance: buy 47.75 Cr shares for Rs 17,770 Cr; post-offer holding 77.0%. BREACHES 75% MPS — must sell down within 12 months or pursue delisting (requires 90%).</t>
+          <t>100% acceptance: buy 47.75 Cr shares for Rs 18,590 Cr; post-offer holding 77.0%. BREACHES 75% MPS — must sell down within 12 months or pursue delisting (requires 90%).</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1925,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deal value Rs 34,856 Cr exceeds the Rs 2,000 Cr deal-value threshold (2024 amendment) — CCI approval required; expect ~150-210 days outer timeline, Green Channel possible if no overlaps.</t>
+          <t>Deal value Rs 36,466 Cr exceeds the Rs 2,000 Cr deal-value threshold (2024 amendment) — CCI approval required; expect ~150-210 days outer timeline, Green Channel possible if no overlaps.</t>
         </is>
       </c>
     </row>
@@ -2209,31 +2221,31 @@
         <v>2</v>
       </c>
       <c r="B4" s="19" t="n">
-        <v>2.17</v>
+        <v>1.18</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>2.5</v>
+        <v>1.52</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>2.84</v>
+        <v>1.86</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>3.17</v>
+        <v>2.19</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>3.51</v>
+        <v>2.53</v>
       </c>
       <c r="G4" s="19" t="n">
-        <v>3.84</v>
+        <v>2.86</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>4.18</v>
+        <v>3.2</v>
       </c>
       <c r="I4" s="19" t="n">
-        <v>4.51</v>
+        <v>3.53</v>
       </c>
       <c r="J4" s="19" t="n">
-        <v>4.85</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="5">
@@ -2241,31 +2253,31 @@
         <v>4.5</v>
       </c>
       <c r="B5" s="19" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E5" s="19" t="n">
         <v>1.65</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="F5" s="19" t="n">
         <v>1.98</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="G5" s="19" t="n">
         <v>2.32</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="H5" s="19" t="n">
         <v>2.65</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="I5" s="19" t="n">
         <v>2.99</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="J5" s="19" t="n">
         <v>3.32</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="I5" s="19" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="J5" s="19" t="n">
-        <v>4.33</v>
       </c>
     </row>
     <row r="6">
@@ -2273,31 +2285,31 @@
         <v>7</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>1.12</v>
+        <v>0.09</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>1.46</v>
+        <v>0.43</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>1.8</v>
+        <v>0.76</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>2.13</v>
+        <v>1.1</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>2.47</v>
+        <v>1.44</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>3.14</v>
+        <v>2.11</v>
       </c>
       <c r="I6" s="19" t="n">
-        <v>3.47</v>
+        <v>2.44</v>
       </c>
       <c r="J6" s="19" t="n">
-        <v>3.81</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="7">
@@ -2305,31 +2317,31 @@
         <v>9.5</v>
       </c>
       <c r="B7" s="19" t="n">
-        <v>0.6</v>
+        <v>-0.45</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.12</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>1.27</v>
+        <v>0.22</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>1.61</v>
+        <v>0.55</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>1.94</v>
+        <v>0.89</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>2.28</v>
+        <v>1.23</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>2.62</v>
+        <v>1.56</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>2.95</v>
+        <v>1.9</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>3.29</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="8">
@@ -2337,31 +2349,31 @@
         <v>12</v>
       </c>
       <c r="B8" s="19" t="n">
-        <v>0.08</v>
+        <v>-1</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>0.42</v>
+        <v>-0.66</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>0.75</v>
+        <v>-0.33</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>1.09</v>
+        <v>0.01</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>1.42</v>
+        <v>0.34</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>1.76</v>
+        <v>0.68</v>
       </c>
       <c r="H8" s="19" t="n">
-        <v>2.09</v>
+        <v>1.02</v>
       </c>
       <c r="I8" s="19" t="n">
-        <v>2.43</v>
+        <v>1.35</v>
       </c>
       <c r="J8" s="19" t="n">
-        <v>2.76</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="9">
@@ -2369,31 +2381,31 @@
         <v>14.5</v>
       </c>
       <c r="B9" s="19" t="n">
-        <v>-0.44</v>
+        <v>-1.54</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>-0.1</v>
+        <v>-1.21</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>0.23</v>
+        <v>-0.87</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>0.57</v>
+        <v>-0.54</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>1.24</v>
+        <v>0.13</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>1.57</v>
+        <v>0.47</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>1.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>2.24</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="10">
@@ -2401,31 +2413,31 @@
         <v>17</v>
       </c>
       <c r="B10" s="19" t="n">
-        <v>-0.96</v>
+        <v>-2.09</v>
       </c>
       <c r="C10" s="19" t="n">
-        <v>-0.62</v>
+        <v>-1.75</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>-0.29</v>
+        <v>-1.42</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>0.05</v>
+        <v>-1.08</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>0.38</v>
+        <v>-0.75</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>0.72</v>
+        <v>-0.41</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>1.05</v>
+        <v>-0.08</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>1.39</v>
+        <v>0.26</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>1.72</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11">
@@ -2433,31 +2445,31 @@
         <v>19.5</v>
       </c>
       <c r="B11" s="19" t="n">
-        <v>-1.48</v>
+        <v>-2.63</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>-1.15</v>
+        <v>-2.3</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.96</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.48</v>
+        <v>-1.63</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.14</v>
+        <v>-1.29</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.2</v>
+        <v>-0.96</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>0.53</v>
+        <v>-0.62</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>0.87</v>
+        <v>-0.29</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>1.2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="12">
@@ -2465,31 +2477,31 @@
         <v>22</v>
       </c>
       <c r="B12" s="19" t="n">
-        <v>-2</v>
+        <v>-3.18</v>
       </c>
       <c r="C12" s="19" t="n">
-        <v>-1.67</v>
+        <v>-2.84</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>-1.33</v>
+        <v>-2.51</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-1</v>
+        <v>-2.17</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-0.66</v>
+        <v>-1.84</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>-0.33</v>
+        <v>-1.5</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>0.01</v>
+        <v>-1.17</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>0.34</v>
+        <v>-0.83</v>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.68</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="14">
@@ -2538,31 +2550,31 @@
         <v>0</v>
       </c>
       <c r="B16" s="19" t="n">
-        <v>1.62</v>
+        <v>0.75</v>
       </c>
       <c r="C16" s="19" t="n">
-        <v>1.12</v>
+        <v>0.24</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>0.63</v>
+        <v>-0.26</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>0.15</v>
+        <v>-0.77</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-0.34</v>
+        <v>-1.26</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.76</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>-1.29</v>
+        <v>-2.25</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>-1.77</v>
+        <v>-2.74</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>-2.24</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="17">
@@ -2570,31 +2582,31 @@
         <v>10</v>
       </c>
       <c r="B17" s="19" t="n">
-        <v>1.78</v>
+        <v>0.9</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>1.29</v>
+        <v>0.39</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>0.79</v>
+        <v>-0.12</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>0.3</v>
+        <v>-0.62</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>-0.18</v>
+        <v>-1.12</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>-0.67</v>
+        <v>-1.62</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>-1.15</v>
+        <v>-2.12</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>-1.63</v>
+        <v>-2.61</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>-2.1</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="18">
@@ -2602,31 +2614,31 @@
         <v>20</v>
       </c>
       <c r="B18" s="19" t="n">
-        <v>1.95</v>
+        <v>1.06</v>
       </c>
       <c r="C18" s="19" t="n">
-        <v>1.45</v>
+        <v>0.55</v>
       </c>
       <c r="D18" s="19" t="n">
-        <v>0.96</v>
+        <v>0.04</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>0.47</v>
+        <v>-0.47</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-0.02</v>
+        <v>-0.98</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>-0.51</v>
+        <v>-1.49</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>-1</v>
+        <v>-1.99</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>-1.48</v>
+        <v>-2.49</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>-1.96</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="19">
@@ -2634,31 +2646,31 @@
         <v>30</v>
       </c>
       <c r="B19" s="19" t="n">
-        <v>2.13</v>
+        <v>1.23</v>
       </c>
       <c r="C19" s="19" t="n">
-        <v>1.63</v>
+        <v>0.71</v>
       </c>
       <c r="D19" s="19" t="n">
-        <v>1.13</v>
+        <v>0.19</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>0.63</v>
+        <v>-0.32</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>0.14</v>
+        <v>-0.83</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>-0.35</v>
+        <v>-1.34</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>-0.84</v>
+        <v>-1.85</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>-1.33</v>
+        <v>-2.35</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>-1.82</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="20">
@@ -2666,31 +2678,31 @@
         <v>40</v>
       </c>
       <c r="B20" s="19" t="n">
-        <v>2.31</v>
+        <v>1.4</v>
       </c>
       <c r="C20" s="19" t="n">
-        <v>1.81</v>
+        <v>0.88</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>1.3</v>
+        <v>0.35</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>0.8</v>
+        <v>-0.16</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>0.31</v>
+        <v>-0.68</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>-0.19</v>
+        <v>-1.19</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.71</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>-1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>-1.67</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="21">
@@ -2698,31 +2710,31 @@
         <v>50</v>
       </c>
       <c r="B21" s="19" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="C21" s="19" t="n">
-        <v>1.99</v>
+        <v>1.05</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>1.48</v>
+        <v>0.52</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>0.98</v>
+        <v>-0</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>0.48</v>
+        <v>-0.52</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>-0.02</v>
+        <v>-1.04</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>-0.52</v>
+        <v>-1.56</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>-1.02</v>
+        <v>-2.08</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>-1.51</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="22">
@@ -2730,31 +2742,31 @@
         <v>60</v>
       </c>
       <c r="B22" s="19" t="n">
-        <v>2.69</v>
+        <v>1.75</v>
       </c>
       <c r="C22" s="19" t="n">
-        <v>2.18</v>
+        <v>1.22</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>1.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>1.16</v>
+        <v>0.17</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>0.65</v>
+        <v>-0.36</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>0.15</v>
+        <v>-0.88</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>-0.35</v>
+        <v>-1.41</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>-0.85</v>
+        <v>-1.93</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>-1.35</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="23">
@@ -2762,31 +2774,31 @@
         <v>70</v>
       </c>
       <c r="B23" s="19" t="n">
-        <v>2.88</v>
+        <v>1.94</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>2.37</v>
+        <v>1.4</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>1.86</v>
+        <v>0.87</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>1.35</v>
+        <v>0.34</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>0.84</v>
+        <v>-0.19</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.33</v>
+        <v>-0.72</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>-0.18</v>
+        <v>-1.25</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>-0.68</v>
+        <v>-1.78</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>-1.19</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="24">
@@ -2794,31 +2806,31 @@
         <v>80</v>
       </c>
       <c r="B24" s="19" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>2.57</v>
+        <v>1.59</v>
       </c>
       <c r="D24" s="19" t="n">
-        <v>2.05</v>
+        <v>1.05</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>1.54</v>
+        <v>0.52</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>1.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>0.51</v>
+        <v>-0.55</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>-0.51</v>
+        <v>-1.62</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>-1.02</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="25">
@@ -2826,31 +2838,31 @@
         <v>90</v>
       </c>
       <c r="B25" s="19" t="n">
-        <v>3.29</v>
+        <v>2.32</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>2.78</v>
+        <v>1.78</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>1.74</v>
+        <v>0.7</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>1.22</v>
+        <v>0.16</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>0.7</v>
+        <v>-0.38</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>0.19</v>
+        <v>-0.92</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>-0.33</v>
+        <v>-1.46</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>-0.84</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="26">
@@ -2858,31 +2870,31 @@
         <v>100</v>
       </c>
       <c r="B26" s="19" t="n">
-        <v>3.51</v>
+        <v>2.53</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>2.99</v>
+        <v>1.98</v>
       </c>
       <c r="D26" s="19" t="n">
-        <v>2.47</v>
+        <v>1.44</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>1.94</v>
+        <v>0.89</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>1.42</v>
+        <v>0.34</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>0.38</v>
+        <v>-0.75</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>-0.14</v>
+        <v>-1.29</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>-0.66</v>
+        <v>-1.84</v>
       </c>
     </row>
   </sheetData>
